--- a/financial_advisor_forms/012_personal_wealth_advisory_recommendations--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/012_personal_wealth_advisory_recommendations--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>client goals</t>
+          <t>What are your main financial goals for the next 12 months?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>risk tolerance</t>
+          <t>How would you rate your overall risk tolerance level (1-6)?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>investment_preferences</t>
+          <t>investment_horizon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>investment preferences</t>
+          <t>What is your investment horizon (e.g., Daily, Weekly, Monthly, Quarterly, Semi-Annually, Annually)?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>investment_preferences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>risk level</t>
+          <t>Which type of investments do you prefer (e.g., Stocks, Bonds, Real Estate, Alternative Investments)?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>investment_horizon</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>investment horizon</t>
+          <t>Do you have any additional comments or concerns about your financial goals or investments?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>investment_frequency</t>
+          <t>risk_tolerance_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>investment frequency</t>
+          <t>What is your risk tolerance level for each type of investment (e.g., Stocks, Bonds, Real Estate, Alternative Investments)?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,85 +658,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>investment_frequency_2</t>
+          <t>investment_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>investment frequency</t>
+          <t>How frequently do you plan to make investments (e.g., Daily, Weekly, Monthly, Quarterly, Semi-Annually, Annually)?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>investment_horizon_2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>investment horizon</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>investment_preferences_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>investment preferences</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>risk tolerance</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,10 +684,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
@@ -883,442 +814,340 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>investment_preferences_choices</t>
+          <t>investment_horizon_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stocks</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>investment_preferences_choices</t>
+          <t>investment_horizon_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bonds</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bonds</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>investment_preferences_choices</t>
+          <t>investment_horizon_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>real_estate</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>investment_preferences_choices</t>
+          <t>investment_horizon_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>alternative_investments</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alternative Investments</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_horizon_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_horizon_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_preferences_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_preferences_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_preferences_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>semi-annually</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Semi-Annually</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_preferences_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>alternative_investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Alternative Investments</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>investment_frequency_2_choices</t>
+          <t>risk_tolerance_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>investment_frequency_2_choices</t>
+          <t>risk_tolerance_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>investment_frequency_2_choices</t>
+          <t>risk_tolerance_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>investment_frequency_2_choices</t>
+          <t>risk_tolerance_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>alternative_investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Alternative Investments</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>investment_frequency_2_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>semi-annually</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Semi-Annually</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>investment_frequency_2_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>investment_preferences_2_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stocks</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>investment_preferences_2_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bonds</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bonds</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>investment_preferences_2_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>real_estate</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>investment_preferences_2_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>alternative_investments</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alternative Investments</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>risk_level_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Risk level 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>risk_level_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Risk level 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>risk_level_3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Risk level 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>risk_level_4</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Risk level 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>risk_level_5</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Risk level 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>risk_tolerance_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>risk_level_6</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Risk level 6</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
